--- a/salidas/empresas/D.xlsx
+++ b/salidas/empresas/D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.13539123535156</v>
+        <v>16.13539886474609</v>
       </c>
       <c r="C3" t="n">
         <v>37.54999923706055</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.8312463760376</v>
+        <v>14.83123970031738</v>
       </c>
       <c r="C4" t="n">
         <v>34.51499938964844</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.08597755432129</v>
+        <v>16.08598327636719</v>
       </c>
       <c r="C5" t="n">
         <v>37.43500137329102</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22373199462891</v>
+        <v>16.22372245788574</v>
       </c>
       <c r="C7" t="n">
         <v>37.39500045776367</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>17.0241756439209</v>
+        <v>17.02417755126953</v>
       </c>
       <c r="C8" t="n">
         <v>39.2400016784668</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>17.47833633422852</v>
+        <v>17.47834968566895</v>
       </c>
       <c r="C9" t="n">
         <v>39.94499969482422</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.73448944091797</v>
+        <v>16.73449516296387</v>
       </c>
       <c r="C10" t="n">
         <v>38.24499893188477</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>17.718994140625</v>
+        <v>17.71899032592773</v>
       </c>
       <c r="C11" t="n">
         <v>40.49499893188477</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.81627464294434</v>
+        <v>17.8162784576416</v>
       </c>
       <c r="C12" t="n">
         <v>40.36999893188477</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>18.50034141540527</v>
+        <v>18.50034523010254</v>
       </c>
       <c r="C13" t="n">
         <v>41.91999816894531</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>18.30615043640137</v>
+        <v>18.30615425109863</v>
       </c>
       <c r="C14" t="n">
         <v>41.47999954223633</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.75068855285645</v>
+        <v>19.75069427490234</v>
       </c>
       <c r="C16" t="n">
         <v>44.3849983215332</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>20.29134750366211</v>
+        <v>20.29134559631348</v>
       </c>
       <c r="C17" t="n">
         <v>45.59999847412109</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>19.87145805358887</v>
+        <v>19.87146759033203</v>
       </c>
       <c r="C18" t="n">
         <v>44.29499816894531</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>18.89123725891113</v>
+        <v>18.89123344421387</v>
       </c>
       <c r="C20" t="n">
         <v>42.11000061035156</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>19.26471519470215</v>
+        <v>19.26471138000488</v>
       </c>
       <c r="C21" t="n">
         <v>42.59000015258789</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>20.72347450256348</v>
+        <v>20.72348213195801</v>
       </c>
       <c r="C23" t="n">
         <v>45.81499862670898</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>21.45479774475098</v>
+        <v>21.45479583740234</v>
       </c>
       <c r="C24" t="n">
         <v>47.22999954223633</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>21.55474281311035</v>
+        <v>21.55473709106445</v>
       </c>
       <c r="C25" t="n">
         <v>47.45000076293945</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>19.53327369689941</v>
+        <v>19.53327560424805</v>
       </c>
       <c r="C26" t="n">
         <v>43</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>18.31243324279785</v>
+        <v>18.31243515014648</v>
       </c>
       <c r="C27" t="n">
         <v>39.93999862670898</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>18.7250862121582</v>
+        <v>18.7250804901123</v>
       </c>
       <c r="C28" t="n">
         <v>40.84000015258789</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>19.89426040649414</v>
+        <v>19.89425849914551</v>
       </c>
       <c r="C29" t="n">
         <v>43.38999938964844</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>21.41439247131348</v>
+        <v>21.41438293457031</v>
       </c>
       <c r="C30" t="n">
         <v>46.29999923706055</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>21.96478080749512</v>
+        <v>21.96478271484375</v>
       </c>
       <c r="C31" t="n">
         <v>47.4900016784668</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>20.43386268615723</v>
+        <v>20.43385314941406</v>
       </c>
       <c r="C32" t="n">
         <v>44.18000030517578</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>19.96529197692871</v>
+        <v>19.96528816223145</v>
       </c>
       <c r="C34" t="n">
         <v>42.77999877929688</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>16.9317626953125</v>
+        <v>16.93176460266113</v>
       </c>
       <c r="C35" t="n">
         <v>36.27999877929688</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.36870384216309</v>
+        <v>17.36869812011719</v>
       </c>
       <c r="C36" t="n">
         <v>36.81999969482422</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.90641403198242</v>
+        <v>16.90641784667969</v>
       </c>
       <c r="C37" t="n">
         <v>35.84000015258789</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>16.5950756072998</v>
+        <v>16.59508514404297</v>
       </c>
       <c r="C38" t="n">
         <v>35.18000030517578</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.43626689910889</v>
+        <v>14.43626594543457</v>
       </c>
       <c r="C39" t="n">
         <v>30.18000030517578</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.82372665405273</v>
+        <v>14.82371807098389</v>
       </c>
       <c r="C40" t="n">
         <v>30.98999977111816</v>
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>15.42046737670898</v>
+        <v>15.42047309875488</v>
       </c>
       <c r="C42" t="n">
         <v>31.79000091552734</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.39546394348145</v>
+        <v>16.39546775817871</v>
       </c>
       <c r="C44" t="n">
         <v>33.79999923706055</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>16.25370979309082</v>
+        <v>16.25370407104492</v>
       </c>
       <c r="C45" t="n">
         <v>33.08000183105469</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>16.95141983032227</v>
+        <v>16.95141410827637</v>
       </c>
       <c r="C46" t="n">
         <v>34.5</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.74996376037598</v>
+        <v>16.74996948242188</v>
       </c>
       <c r="C47" t="n">
         <v>34.09000015258789</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.0894603729248</v>
+        <v>18.08945655822754</v>
       </c>
       <c r="C48" t="n">
         <v>36.38000106811523</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.35244560241699</v>
+        <v>19.35244941711426</v>
       </c>
       <c r="C49" t="n">
         <v>38.91999816894531</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.62647819519043</v>
+        <v>18.6264820098877</v>
       </c>
       <c r="C50" t="n">
         <v>37.45999908447266</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>19.11553955078125</v>
+        <v>19.11553764343262</v>
       </c>
       <c r="C51" t="n">
         <v>37.9900016784668</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.68544387817383</v>
+        <v>20.6854362487793</v>
       </c>
       <c r="C52" t="n">
         <v>41.11000061035156</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>21.03262329101562</v>
+        <v>21.03262710571289</v>
       </c>
       <c r="C53" t="n">
         <v>41.79999923706055</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>19.83518028259277</v>
+        <v>19.83519172668457</v>
       </c>
       <c r="C54" t="n">
         <v>38.95999908447266</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>19.72317695617676</v>
+        <v>19.72318458557129</v>
       </c>
       <c r="C55" t="n">
         <v>38.7400016784668</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>21.37782669067383</v>
+        <v>21.3778133392334</v>
       </c>
       <c r="C56" t="n">
         <v>41.9900016784668</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>21.98124694824219</v>
+        <v>21.98125076293945</v>
       </c>
       <c r="C57" t="n">
         <v>42.72999954223633</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>22.45965957641602</v>
+        <v>22.45966529846191</v>
       </c>
       <c r="C58" t="n">
         <v>43.65999984741211</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>22.35677337646484</v>
+        <v>22.35677528381348</v>
       </c>
       <c r="C59" t="n">
         <v>43.45999908447266</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>21.59673118591309</v>
+        <v>21.59674263000488</v>
       </c>
       <c r="C60" t="n">
         <v>41.52999877929688</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>22.21556091308594</v>
+        <v>22.21557235717773</v>
       </c>
       <c r="C61" t="n">
         <v>42.72000122070312</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>22.6419792175293</v>
+        <v>22.64198875427246</v>
       </c>
       <c r="C62" t="n">
         <v>43.54000091552734</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>23.72884750366211</v>
+        <v>23.72884368896484</v>
       </c>
       <c r="C63" t="n">
         <v>45.63000106811523</v>
@@ -1780,11 +1792,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>23.49945640563965</v>
+        <v>23.49944114685059</v>
       </c>
       <c r="C64" t="n">
         <v>44.70000076293945</v>
@@ -1805,11 +1817,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>24.4036750793457</v>
+        <v>24.40368270874023</v>
       </c>
       <c r="C65" t="n">
         <v>46.41999816894531</v>
@@ -1834,11 +1846,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>25.34794998168945</v>
+        <v>25.34794235229492</v>
       </c>
       <c r="C66" t="n">
         <v>47.72000122070312</v>
@@ -1863,11 +1875,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>25.64009094238281</v>
+        <v>25.64008331298828</v>
       </c>
       <c r="C67" t="n">
         <v>48.27000045776367</v>
@@ -1892,11 +1904,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>25.7357006072998</v>
+        <v>25.7357063293457</v>
       </c>
       <c r="C68" t="n">
         <v>48.45000076293945</v>
@@ -1921,11 +1933,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>26.15234756469727</v>
+        <v>26.15233039855957</v>
       </c>
       <c r="C69" t="n">
         <v>48.7400016784668</v>
@@ -1950,11 +1962,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>27.2415657043457</v>
+        <v>27.24157333374023</v>
       </c>
       <c r="C70" t="n">
         <v>50.77000045776367</v>
@@ -1979,11 +1991,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>27.68155479431152</v>
+        <v>27.68156051635742</v>
       </c>
       <c r="C71" t="n">
         <v>51.59000015258789</v>
@@ -2008,11 +2020,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.96881294250488</v>
+        <v>27.96881866455078</v>
       </c>
       <c r="C72" t="n">
         <v>51.61999893188477</v>
@@ -2037,11 +2049,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>28.75987243652344</v>
+        <v>28.75988578796387</v>
       </c>
       <c r="C73" t="n">
         <v>53.08000183105469</v>
@@ -2066,11 +2078,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>27.11273765563965</v>
+        <v>27.11273956298828</v>
       </c>
       <c r="C74" t="n">
         <v>50.04000091552734</v>
@@ -2095,7 +2107,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2124,11 +2136,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>28.03549385070801</v>
+        <v>28.0355052947998</v>
       </c>
       <c r="C76" t="n">
         <v>51.20999908447266</v>
@@ -2153,11 +2165,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>28.57201385498047</v>
+        <v>28.5720100402832</v>
       </c>
       <c r="C77" t="n">
         <v>52.18999862670898</v>
@@ -2182,11 +2194,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>28.79039764404297</v>
+        <v>28.79038429260254</v>
       </c>
       <c r="C78" t="n">
         <v>52.06000137329102</v>
@@ -2211,11 +2223,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>29.86326789855957</v>
+        <v>29.86326026916504</v>
       </c>
       <c r="C79" t="n">
         <v>54</v>
@@ -2240,7 +2252,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2269,11 +2281,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>29.30951309204102</v>
+        <v>29.30951118469238</v>
       </c>
       <c r="C81" t="n">
         <v>52.47999954223633</v>
@@ -2298,11 +2310,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>29.56641960144043</v>
+        <v>29.56641578674316</v>
       </c>
       <c r="C82" t="n">
         <v>52.93999862670898</v>
@@ -2327,11 +2339,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>29.47705841064453</v>
+        <v>29.47707176208496</v>
       </c>
       <c r="C83" t="n">
         <v>52.77999877929688</v>
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2385,11 +2397,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>29.23457908630371</v>
+        <v>29.23457717895508</v>
       </c>
       <c r="C85" t="n">
         <v>51.79999923706055</v>
@@ -2414,11 +2426,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>30.53827476501465</v>
+        <v>30.53828620910645</v>
       </c>
       <c r="C86" t="n">
         <v>54.11000061035156</v>
@@ -2443,11 +2455,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>31.9276008605957</v>
+        <v>31.92761039733887</v>
       </c>
       <c r="C87" t="n">
         <v>56</v>
@@ -2472,11 +2484,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>33.17049789428711</v>
+        <v>33.17050170898438</v>
       </c>
       <c r="C88" t="n">
         <v>58.18000030517578</v>
@@ -2501,11 +2513,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>35.16598510742188</v>
+        <v>35.16598129272461</v>
       </c>
       <c r="C89" t="n">
         <v>61.68000030517578</v>
@@ -2530,11 +2542,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>32.24119186401367</v>
+        <v>32.24117660522461</v>
       </c>
       <c r="C90" t="n">
         <v>56.54999923706055</v>
@@ -2559,11 +2571,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>32.72614669799805</v>
+        <v>32.72615051269531</v>
       </c>
       <c r="C91" t="n">
         <v>56.81999969482422</v>
@@ -2588,11 +2600,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>34.16028213500977</v>
+        <v>34.1602897644043</v>
       </c>
       <c r="C92" t="n">
         <v>59.31000137329102</v>
@@ -2617,11 +2629,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>33.60736846923828</v>
+        <v>33.60735702514648</v>
       </c>
       <c r="C93" t="n">
         <v>58.34999847412109</v>
@@ -2646,11 +2658,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>36.34017944335938</v>
+        <v>36.34017562866211</v>
       </c>
       <c r="C94" t="n">
         <v>62.47999954223633</v>
@@ -2675,11 +2687,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>37.0788459777832</v>
+        <v>37.07884979248047</v>
       </c>
       <c r="C95" t="n">
         <v>63.75</v>
@@ -2704,11 +2716,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>37.7535285949707</v>
+        <v>37.7535400390625</v>
       </c>
       <c r="C96" t="n">
         <v>64.91000366210938</v>
@@ -2733,7 +2745,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2762,7 +2774,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2791,11 +2803,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>41.06464385986328</v>
+        <v>41.06462478637695</v>
       </c>
       <c r="C99" t="n">
         <v>69.40000152587891</v>
@@ -2820,11 +2832,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>42.00545501708984</v>
+        <v>42.00545883178711</v>
       </c>
       <c r="C100" t="n">
         <v>70.98999786376953</v>
@@ -2849,11 +2861,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>42.92261505126953</v>
+        <v>42.92262649536133</v>
       </c>
       <c r="C101" t="n">
         <v>72.54000091552734</v>
@@ -2878,11 +2890,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>41.1600341796875</v>
+        <v>41.16003036499023</v>
       </c>
       <c r="C102" t="n">
         <v>68.95999908447266</v>
@@ -2907,11 +2919,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>42.68800735473633</v>
+        <v>42.68801879882812</v>
       </c>
       <c r="C103" t="n">
         <v>71.51999664306641</v>
@@ -2936,11 +2948,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>40.37216567993164</v>
+        <v>40.37217712402344</v>
       </c>
       <c r="C104" t="n">
         <v>67.63999938964844</v>
@@ -2965,11 +2977,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>42.27744293212891</v>
+        <v>42.27743530273438</v>
       </c>
       <c r="C105" t="n">
         <v>70.22000122070312</v>
@@ -2994,11 +3006,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>41.59709930419922</v>
+        <v>41.59710311889648</v>
       </c>
       <c r="C106" t="n">
         <v>69.08999633789062</v>
@@ -3023,11 +3035,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>42.92768859863281</v>
+        <v>42.92768478393555</v>
       </c>
       <c r="C107" t="n">
         <v>71.30000305175781</v>
@@ -3052,11 +3064,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>44.04202651977539</v>
+        <v>44.04201889038086</v>
       </c>
       <c r="C108" t="n">
         <v>72.55000305175781</v>
@@ -3081,7 +3093,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3110,11 +3122,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>46.67663955688477</v>
+        <v>46.67665863037109</v>
       </c>
       <c r="C110" t="n">
         <v>76.88999938964844</v>
@@ -3139,11 +3151,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>44.14905548095703</v>
+        <v>44.14904403686523</v>
       </c>
       <c r="C111" t="n">
         <v>72.08999633789062</v>
@@ -3168,11 +3180,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>43.40190505981445</v>
+        <v>43.40190887451172</v>
       </c>
       <c r="C112" t="n">
         <v>70.87000274658203</v>
@@ -3197,11 +3209,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>43.89797973632812</v>
+        <v>43.89797210693359</v>
       </c>
       <c r="C113" t="n">
         <v>71.68000030517578</v>
@@ -3226,11 +3238,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>43.58248519897461</v>
+        <v>43.58249282836914</v>
       </c>
       <c r="C114" t="n">
         <v>70.51999664306641</v>
@@ -3255,11 +3267,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>41.32673645019531</v>
+        <v>41.32674789428711</v>
       </c>
       <c r="C115" t="n">
         <v>66.87000274658203</v>
@@ -3284,11 +3296,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>44.311767578125</v>
+        <v>44.31175231933594</v>
       </c>
       <c r="C116" t="n">
         <v>71.69999694824219</v>
@@ -3313,11 +3325,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>43.508056640625</v>
+        <v>43.50806427001953</v>
       </c>
       <c r="C117" t="n">
         <v>69.75</v>
@@ -3342,11 +3354,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>43.90104293823242</v>
+        <v>43.90103530883789</v>
       </c>
       <c r="C118" t="n">
         <v>70.37999725341797</v>
@@ -3371,11 +3383,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>44.55598831176758</v>
+        <v>44.55599212646484</v>
       </c>
       <c r="C119" t="n">
         <v>71.43000030517578</v>
@@ -3400,11 +3412,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>42.42189025878906</v>
+        <v>42.4218864440918</v>
       </c>
       <c r="C120" t="n">
         <v>67.37000274658203</v>
@@ -3429,11 +3441,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>42.59189224243164</v>
+        <v>42.59188461303711</v>
       </c>
       <c r="C121" t="n">
         <v>67.63999938964844</v>
@@ -3458,11 +3470,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>45.44438171386719</v>
+        <v>45.44436645507812</v>
       </c>
       <c r="C122" t="n">
         <v>72.16999816894531</v>
@@ -3487,11 +3499,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>44.02758407592773</v>
+        <v>44.02758026123047</v>
       </c>
       <c r="C123" t="n">
         <v>69.91999816894531</v>
@@ -3516,11 +3528,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>47.78007507324219</v>
+        <v>47.78009033203125</v>
       </c>
       <c r="C124" t="n">
         <v>75.12000274658203</v>
@@ -3545,11 +3557,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>45.45851135253906</v>
+        <v>45.4585075378418</v>
       </c>
       <c r="C125" t="n">
         <v>71.47000122070312</v>
@@ -3574,11 +3586,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>45.95462417602539</v>
+        <v>45.95461654663086</v>
       </c>
       <c r="C126" t="n">
         <v>72.25</v>
@@ -3603,11 +3615,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>50.05233383178711</v>
+        <v>50.05231475830078</v>
       </c>
       <c r="C127" t="n">
         <v>77.93000030517578</v>
@@ -3632,11 +3644,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>50.110107421875</v>
+        <v>50.11013412475586</v>
       </c>
       <c r="C128" t="n">
         <v>78.01999664306641</v>
@@ -3661,11 +3673,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>48.08000564575195</v>
+        <v>48.07998657226562</v>
       </c>
       <c r="C129" t="n">
         <v>74.16000366210938</v>
@@ -3690,11 +3702,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>48.15129470825195</v>
+        <v>48.15131378173828</v>
       </c>
       <c r="C130" t="n">
         <v>74.26999664306641</v>
@@ -3719,11 +3731,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>48.75424575805664</v>
+        <v>48.75425338745117</v>
       </c>
       <c r="C131" t="n">
         <v>75.19999694824219</v>
@@ -3748,11 +3760,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>47.95703506469727</v>
+        <v>47.95702743530273</v>
       </c>
       <c r="C132" t="n">
         <v>73.29000091552734</v>
@@ -3777,11 +3789,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>50.11637496948242</v>
+        <v>50.11635208129883</v>
       </c>
       <c r="C133" t="n">
         <v>76.58999633789062</v>
@@ -3806,7 +3818,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3835,11 +3847,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>50.80343627929688</v>
+        <v>50.80342483520508</v>
       </c>
       <c r="C135" t="n">
         <v>77.63999938964844</v>
@@ -3864,7 +3876,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3893,11 +3905,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>51.16355895996094</v>
+        <v>51.16355133056641</v>
       </c>
       <c r="C137" t="n">
         <v>77.43000030517578</v>
@@ -3922,11 +3934,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>53.8725471496582</v>
+        <v>53.87254333496094</v>
       </c>
       <c r="C138" t="n">
         <v>80.76999664306641</v>
@@ -3951,11 +3963,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>51.11123275756836</v>
+        <v>51.11121368408203</v>
       </c>
       <c r="C139" t="n">
         <v>76.62999725341797</v>
@@ -3980,11 +3992,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>51.47806930541992</v>
+        <v>51.47806549072266</v>
       </c>
       <c r="C140" t="n">
         <v>77.18000030517578</v>
@@ -4009,11 +4021,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>53.03761291503906</v>
+        <v>53.03762817382812</v>
       </c>
       <c r="C141" t="n">
         <v>78.76999664306641</v>
@@ -4038,11 +4050,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>51.79872131347656</v>
+        <v>51.7987060546875</v>
       </c>
       <c r="C142" t="n">
         <v>76.93000030517578</v>
@@ -4067,11 +4079,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>54.63339996337891</v>
+        <v>54.63340377807617</v>
       </c>
       <c r="C143" t="n">
         <v>81.13999938964844</v>
@@ -4096,11 +4108,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>57.17068862915039</v>
+        <v>57.17068099975586</v>
       </c>
       <c r="C144" t="n">
         <v>84.12999725341797</v>
@@ -4125,7 +4137,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4154,11 +4166,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>51.94494247436523</v>
+        <v>51.94493865966797</v>
       </c>
       <c r="C146" t="n">
         <v>76.44000244140625</v>
@@ -4183,11 +4195,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>50.33439636230469</v>
+        <v>50.33440399169922</v>
       </c>
       <c r="C147" t="n">
         <v>74.06999969482422</v>
@@ -4212,11 +4224,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>46.34461975097656</v>
+        <v>46.34463500976562</v>
       </c>
       <c r="C148" t="n">
         <v>67.43000030517578</v>
@@ -4241,11 +4253,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>45.74668121337891</v>
+        <v>45.74667358398438</v>
       </c>
       <c r="C149" t="n">
         <v>66.55999755859375</v>
@@ -4270,11 +4282,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>44.69622421264648</v>
+        <v>44.69621276855469</v>
       </c>
       <c r="C150" t="n">
         <v>64.19000244140625</v>
@@ -4299,11 +4311,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>47.47449111938477</v>
+        <v>47.47449493408203</v>
       </c>
       <c r="C151" t="n">
         <v>68.18000030517578</v>
@@ -4328,11 +4340,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>49.93247222900391</v>
+        <v>49.93248748779297</v>
       </c>
       <c r="C152" t="n">
         <v>71.70999908447266</v>
@@ -4357,11 +4369,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>49.27795028686523</v>
+        <v>49.27795791625977</v>
       </c>
       <c r="C153" t="n">
         <v>70.76999664306641</v>
@@ -4386,11 +4398,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>49.50733947753906</v>
+        <v>49.50734710693359</v>
       </c>
       <c r="C154" t="n">
         <v>70.27999877929688</v>
@@ -4415,11 +4427,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>50.31039047241211</v>
+        <v>50.31039810180664</v>
       </c>
       <c r="C155" t="n">
         <v>71.41999816894531</v>
@@ -4444,11 +4456,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>52.48003005981445</v>
+        <v>52.48002624511719</v>
       </c>
       <c r="C156" t="n">
         <v>74.5</v>
@@ -4473,11 +4485,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>50.90287780761719</v>
+        <v>50.90288162231445</v>
       </c>
       <c r="C157" t="n">
         <v>71.45999908447266</v>
@@ -4502,11 +4514,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>50.03384399414062</v>
+        <v>50.03383255004883</v>
       </c>
       <c r="C158" t="n">
         <v>70.23999786376953</v>
@@ -4531,7 +4543,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4560,7 +4572,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4589,11 +4601,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>56.16251754760742</v>
+        <v>56.16250610351562</v>
       </c>
       <c r="C161" t="n">
         <v>77.87000274658203</v>
@@ -4618,11 +4630,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>54.22238922119141</v>
+        <v>54.22240829467773</v>
       </c>
       <c r="C162" t="n">
         <v>75.18000030517578</v>
@@ -4647,7 +4659,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4676,11 +4688,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>54.22185516357422</v>
+        <v>54.22185897827148</v>
       </c>
       <c r="C164" t="n">
         <v>74.29000091552734</v>
@@ -4705,11 +4717,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>56.65963363647461</v>
+        <v>56.65961074829102</v>
       </c>
       <c r="C165" t="n">
         <v>77.62999725341797</v>
@@ -4734,11 +4746,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>59.84254455566406</v>
+        <v>59.84254837036133</v>
       </c>
       <c r="C166" t="n">
         <v>81.04000091552734</v>
@@ -4763,7 +4775,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4792,11 +4804,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>61.37106704711914</v>
+        <v>61.3710823059082</v>
       </c>
       <c r="C168" t="n">
         <v>83.11000061035156</v>
@@ -4821,11 +4833,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>61.84722900390625</v>
+        <v>61.84721755981445</v>
       </c>
       <c r="C169" t="n">
         <v>82.81999969482422</v>
@@ -4850,11 +4862,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>64.03524780273438</v>
+        <v>64.03525543212891</v>
       </c>
       <c r="C170" t="n">
         <v>85.75</v>
@@ -4879,7 +4891,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4908,11 +4920,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>54.49949645996094</v>
+        <v>54.49948883056641</v>
       </c>
       <c r="C172" t="n">
         <v>72.19000244140625</v>
@@ -4937,11 +4949,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>58.22893905639648</v>
+        <v>58.22892379760742</v>
       </c>
       <c r="C173" t="n">
         <v>77.12999725341797</v>
@@ -4966,7 +4978,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4995,11 +5007,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>61.95993423461914</v>
+        <v>61.95994186401367</v>
       </c>
       <c r="C175" t="n">
         <v>81.18000030517578</v>
@@ -5024,11 +5036,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>61.84545135498047</v>
+        <v>61.84543609619141</v>
       </c>
       <c r="C176" t="n">
         <v>81.02999877929688</v>
@@ -5053,11 +5065,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>59.86865615844727</v>
+        <v>59.8686637878418</v>
       </c>
       <c r="C177" t="n">
         <v>78.44000244140625</v>
@@ -5082,11 +5094,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>60.9625358581543</v>
+        <v>60.96255493164062</v>
       </c>
       <c r="C178" t="n">
         <v>78.93000030517578</v>
@@ -5111,11 +5123,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>62.05157470703125</v>
+        <v>62.05157089233398</v>
       </c>
       <c r="C179" t="n">
         <v>80.33999633789062</v>
@@ -5140,11 +5152,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>60.62270736694336</v>
+        <v>60.62272262573242</v>
       </c>
       <c r="C180" t="n">
         <v>78.48999786376953</v>
@@ -5167,7 +5179,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5194,7 +5206,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5221,11 +5233,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>53.18515777587891</v>
+        <v>53.18517303466797</v>
       </c>
       <c r="C183" t="n">
         <v>68.31999969482422</v>
@@ -5248,11 +5260,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>59.67296981811523</v>
+        <v>59.67296600341797</v>
       </c>
       <c r="C184" t="n">
         <v>75.95999908447266</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>62.76817321777344</v>
+        <v>62.76816940307617</v>
       </c>
       <c r="C185" t="n">
         <v>79.90000152587891</v>
@@ -5302,11 +5314,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>59.81437683105469</v>
+        <v>59.81438446044922</v>
       </c>
       <c r="C186" t="n">
         <v>76.13999938964844</v>
@@ -5331,11 +5343,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>58.27604675292969</v>
+        <v>58.27603530883789</v>
       </c>
       <c r="C187" t="n">
         <v>73.56999969482422</v>
@@ -5360,11 +5372,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>59.30580139160156</v>
+        <v>59.30579376220703</v>
       </c>
       <c r="C188" t="n">
         <v>74.87000274658203</v>
@@ -5389,11 +5401,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>61.65837478637695</v>
+        <v>61.65838623046875</v>
       </c>
       <c r="C189" t="n">
         <v>77.83999633789062</v>
@@ -5418,11 +5430,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>58.30545425415039</v>
+        <v>58.30545806884766</v>
       </c>
       <c r="C190" t="n">
         <v>73.01999664306641</v>
@@ -5447,7 +5459,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5476,7 +5488,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5505,11 +5517,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>63.29187393188477</v>
+        <v>63.29186248779297</v>
       </c>
       <c r="C193" t="n">
         <v>78.55999755859375</v>
@@ -5534,7 +5546,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5563,11 +5575,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>64.07334136962891</v>
+        <v>64.07334899902344</v>
       </c>
       <c r="C195" t="n">
         <v>79.52999877929688</v>
@@ -5592,7 +5604,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5621,7 +5633,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5650,7 +5662,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5679,11 +5691,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>65.36083221435547</v>
+        <v>65.36082458496094</v>
       </c>
       <c r="C199" t="n">
         <v>79.80999755859375</v>
@@ -5708,11 +5720,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>67.13797760009766</v>
+        <v>67.13798522949219</v>
       </c>
       <c r="C200" t="n">
         <v>81.98000335693359</v>
@@ -5737,11 +5749,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>66.99054718017578</v>
+        <v>66.99056243896484</v>
       </c>
       <c r="C201" t="n">
         <v>81.80000305175781</v>
@@ -5766,7 +5778,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5795,11 +5807,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>57.77410888671875</v>
+        <v>57.77410125732422</v>
       </c>
       <c r="C203" t="n">
         <v>69.97000122070312</v>
@@ -5824,7 +5836,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5853,7 +5865,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5882,7 +5894,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5911,11 +5923,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>46.43290710449219</v>
+        <v>46.43289947509766</v>
       </c>
       <c r="C207" t="n">
         <v>55.61999893188477</v>
@@ -5940,11 +5952,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>47.25162506103516</v>
+        <v>47.25161743164062</v>
       </c>
       <c r="C208" t="n">
         <v>55.90999984741211</v>
@@ -5969,11 +5981,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>48.29113006591797</v>
+        <v>48.29114532470703</v>
       </c>
       <c r="C209" t="n">
         <v>57.13999938964844</v>
@@ -5998,11 +6010,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>42.49349975585938</v>
+        <v>42.49349594116211</v>
       </c>
       <c r="C210" t="n">
         <v>50.27999877929688</v>
@@ -6027,11 +6039,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>44.3589973449707</v>
+        <v>44.35899353027344</v>
       </c>
       <c r="C211" t="n">
         <v>51.79000091552734</v>
@@ -6056,7 +6068,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6085,7 +6097,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6114,11 +6126,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>38.78398513793945</v>
+        <v>38.78397750854492</v>
       </c>
       <c r="C214" t="n">
         <v>44.66999816894531</v>
@@ -6143,11 +6155,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>35.00716400146484</v>
+        <v>35.00716018676758</v>
       </c>
       <c r="C215" t="n">
         <v>40.31999969482422</v>
@@ -6172,11 +6184,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>39.93658828735352</v>
+        <v>39.93659210205078</v>
       </c>
       <c r="C216" t="n">
         <v>45.34000015258789</v>
@@ -6201,11 +6213,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>41.39875793457031</v>
+        <v>41.39875411987305</v>
       </c>
       <c r="C217" t="n">
         <v>47</v>
@@ -6230,11 +6242,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>40.27130126953125</v>
+        <v>40.27129745483398</v>
       </c>
       <c r="C218" t="n">
         <v>45.72000122070312</v>
@@ -6259,7 +6271,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6288,11 +6300,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>43.93476104736328</v>
+        <v>43.93475723266602</v>
       </c>
       <c r="C220" t="n">
         <v>49.18999862670898</v>
@@ -6317,11 +6329,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>45.53352355957031</v>
+        <v>45.53351974487305</v>
       </c>
       <c r="C221" t="n">
         <v>50.97999954223633</v>
@@ -6346,11 +6358,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>48.76834106445312</v>
+        <v>48.76834487915039</v>
       </c>
       <c r="C222" t="n">
         <v>53.91999816894531</v>
@@ -6375,11 +6387,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>44.31841278076172</v>
+        <v>44.31842422485352</v>
       </c>
       <c r="C223" t="n">
         <v>49</v>
@@ -6404,11 +6416,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>48.352294921875</v>
+        <v>48.35229873657227</v>
       </c>
       <c r="C224" t="n">
         <v>53.45999908447266</v>
@@ -6433,11 +6445,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>51.16823196411133</v>
+        <v>51.16823959350586</v>
       </c>
       <c r="C225" t="n">
         <v>55.90000152587891</v>
@@ -6462,11 +6474,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>52.89825057983398</v>
+        <v>52.89824676513672</v>
       </c>
       <c r="C226" t="n">
         <v>57.79000091552734</v>
@@ -6491,11 +6503,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>54.49095916748047</v>
+        <v>54.490966796875</v>
       </c>
       <c r="C227" t="n">
         <v>59.52999877929688</v>
@@ -6520,11 +6532,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>54.38552474975586</v>
+        <v>54.38553237915039</v>
       </c>
       <c r="C228" t="n">
         <v>58.75</v>
@@ -6549,7 +6561,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6578,11 +6590,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>51.46028137207031</v>
+        <v>51.46027755737305</v>
       </c>
       <c r="C230" t="n">
         <v>55.59000015258789</v>
@@ -6607,7 +6619,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6636,7 +6648,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6665,11 +6677,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>50.94267654418945</v>
+        <v>50.94268035888672</v>
       </c>
       <c r="C233" t="n">
         <v>54.38000106811523</v>
@@ -6694,11 +6706,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>53.730224609375</v>
+        <v>53.73022842407227</v>
       </c>
       <c r="C234" t="n">
         <v>56.66999816894531</v>
@@ -6723,7 +6735,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6752,7 +6764,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6781,7 +6793,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6810,11 +6822,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>58.66334533691406</v>
+        <v>58.66335296630859</v>
       </c>
       <c r="C238" t="n">
         <v>61.16999816894531</v>
@@ -6839,7 +6851,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6868,7 +6880,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6897,11 +6909,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>56.82340240478516</v>
+        <v>56.82339859008789</v>
       </c>
       <c r="C241" t="n">
         <v>58.59000015258789</v>
@@ -6926,11 +6938,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>58.35576248168945</v>
+        <v>58.35575866699219</v>
       </c>
       <c r="C242" t="n">
         <v>60.16999816894531</v>
@@ -6955,7 +6967,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6984,7 +6996,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7013,11 +7025,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>63.22185516357422</v>
+        <v>63.22185134887695</v>
       </c>
       <c r="C245" t="n">
         <v>64.5</v>
@@ -7042,7 +7054,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7071,7 +7083,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7100,7 +7112,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7129,7 +7141,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7158,32 +7170,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>61.16999816894531</v>
+        <v>60.40000152587891</v>
       </c>
       <c r="C250" t="n">
-        <v>61.16999816894531</v>
+        <v>60.40000152587891</v>
       </c>
       <c r="D250" t="n">
-        <v>83721700</v>
+        <v>88771200</v>
       </c>
       <c r="E250" t="n">
         <v>2.87</v>
       </c>
       <c r="F250" t="n">
-        <v>21.31358821217607</v>
+        <v>21.04529669891251</v>
       </c>
       <c r="G250" t="n">
         <v>879455403</v>
       </c>
       <c r="H250" t="n">
-        <v>53796285391.17906</v>
+        <v>53119107683.14245</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09519720922107974</v>
+        <v>0.100938830664049</v>
       </c>
     </row>
   </sheetData>
@@ -7215,75 +7227,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7319,13 +7331,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7361,13 +7373,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7403,13 +7415,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7445,13 +7457,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7487,13 +7499,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7529,13 +7541,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7571,13 +7583,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7604,7 +7616,7 @@
       <c r="I9" t="n">
         <v>4.752679233849327</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="K9" t="n">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I10" t="n">
         <v>5.282679233849327</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="K10" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I11" t="n">
         <v>2.884999152685985</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="K11" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I12" t="n">
         <v>2.594999152685985</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="K12" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I13" t="n">
         <v>2.45</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K13" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I14" t="n">
         <v>2.49</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K14" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I15" t="n">
         <v>2.36</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K15" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I16" t="n">
         <v>2.03</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="K16" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I17" t="n">
         <v>0.52</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K17" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I18" t="n">
         <v>0.52</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K18" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I19" t="n">
         <v>0.42</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K19" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I20" t="n">
         <v>1.04</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K20" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I21" t="n">
         <v>2.93</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K21" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I22" t="n">
         <v>2.72</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K22" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I23" t="n">
         <v>2.64</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K23" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I24" t="n">
         <v>2.56</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K24" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I25" t="n">
         <v>2.24</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K25" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I26" t="n">
         <v>2.498628581115443</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="K26" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I27" t="n">
         <v>2.928628581115444</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K27" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I28" t="n">
         <v>3.028628581115443</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="K28" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I29" t="n">
         <v>3.208628581115443</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K29" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I30" t="n">
         <v>3.175961216984286</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K30" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I31" t="n">
         <v>3.205961216984286</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K31" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I32" t="n">
         <v>3.305961216984286</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="K32" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I33" t="n">
         <v>3.435961216984286</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K33" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I34" t="n">
         <v>3.57</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K34" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I35" t="n">
         <v>3.46</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K35" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I36" t="n">
         <v>3.39</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K36" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I37" t="n">
         <v>4.7</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K37" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I38" t="n">
         <v>4.460000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K38" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I39" t="n">
         <v>4.53</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K39" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I40" t="n">
         <v>4.8</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K40" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I41" t="n">
         <v>3.73</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="K41" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I42" t="n">
         <v>2.1</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K42" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I43" t="n">
         <v>1.46</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K43" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I44" t="n">
         <v>1.33</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K44" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I45" t="n">
         <v>1.57</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="K45" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I46" t="n">
         <v>2.09</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K46" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I47" t="n">
         <v>0.6299999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K47" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I48" t="n">
         <v>-0.1300000000000001</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="K48" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I49" t="n">
         <v>-0.5200000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K49" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I50" t="n">
         <v>1.05</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K50" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I51" t="n">
         <v>2.79</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K51" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I52" t="n">
         <v>3.17</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K52" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I53" t="n">
         <v>3.98</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K53" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I54" t="n">
         <v>3.58</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K54" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I55" t="n">
         <v>2.67</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="K55" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I56" t="n">
         <v>2.79</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K56" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I57" t="n">
         <v>1.09</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K57" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I58" t="n">
         <v>1.43</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K58" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I59" t="n">
         <v>2.7</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K59" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I60" t="n">
         <v>1.96</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="K60" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I61" t="n">
         <v>2.329999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K61" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I62" t="n">
         <v>1.94</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K62" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I63" t="n">
         <v>1.9</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K63" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I64" t="n">
         <v>2.85</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K64" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I65" t="n">
         <v>2.7</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K65" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I66" t="n">
         <v>2.67</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K66" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I67" t="n">
         <v>2.9</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K67" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I68" t="n">
         <v>2.94</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K68" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I69" t="n">
         <v>3.44</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="K69" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I70" t="n">
         <v>3.38</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K70" t="n">
@@ -10423,13 +10435,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10450,7 +10462,7 @@
       <c r="I71" t="n">
         <v>2.87</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K71" t="n">
@@ -10487,52 +10499,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="C2" t="n">
@@ -10561,10 +10573,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="C3" t="n">
@@ -10593,10 +10605,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10625,10 +10637,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="C5" t="n">
@@ -10657,10 +10669,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="C6" t="n">
@@ -10689,10 +10701,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="C7" t="n">
@@ -10721,10 +10733,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10753,10 +10765,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="C9" t="n">
@@ -10785,10 +10797,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="C10" t="n">
@@ -10817,10 +10829,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C11" t="n">
@@ -10849,10 +10861,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C12" t="n">
@@ -10881,10 +10893,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C13" t="n">
@@ -10913,10 +10925,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="C14" t="n">
@@ -10945,10 +10957,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C15" t="n">
@@ -10977,10 +10989,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C16" t="n">
@@ -11009,10 +11021,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C17" t="n">
@@ -11041,10 +11053,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C18" t="n">
@@ -11073,10 +11085,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C19" t="n">
@@ -11105,10 +11117,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="C20" t="n">
@@ -11137,10 +11149,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C21" t="n">
@@ -11169,10 +11181,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C22" t="n">
@@ -11201,10 +11213,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C23" t="n">
@@ -11233,10 +11245,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="C24" t="n">
@@ -11265,10 +11277,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C25" t="n">
@@ -11297,10 +11309,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="C26" t="n">
@@ -11329,10 +11341,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C27" t="n">
@@ -11361,10 +11373,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C28" t="n">
@@ -11393,10 +11405,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C29" t="n">
@@ -11425,10 +11437,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42658</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="C30" t="n">
@@ -11457,10 +11469,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42781</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C31" t="n">
@@ -11489,10 +11501,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42839</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C32" t="n">
@@ -11521,10 +11533,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42930</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C33" t="n">
@@ -11553,10 +11565,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43021</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C34" t="n">
@@ -11585,10 +11597,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43146</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C35" t="n">
@@ -11617,10 +11629,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43203</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C36" t="n">
@@ -11649,10 +11661,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43294</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C37" t="n">
@@ -11681,10 +11693,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43385</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C38" t="n">
@@ -11713,10 +11725,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="C39" t="n">
@@ -11745,10 +11757,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43567</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C40" t="n">
@@ -11777,10 +11789,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43658</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C41" t="n">
@@ -11809,10 +11821,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43749</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C42" t="n">
@@ -11841,10 +11853,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43875</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="C43" t="n">
@@ -11873,10 +11885,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43938</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C44" t="n">
@@ -11905,10 +11917,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C45" t="n">
@@ -11937,10 +11949,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="C46" t="n">
@@ -11969,10 +11981,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C47" t="n">
@@ -12001,10 +12013,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C48" t="n">
@@ -12033,10 +12045,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C49" t="n">
@@ -12065,10 +12077,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C50" t="n">
@@ -12097,10 +12109,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C51" t="n">
@@ -12129,10 +12141,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44679</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C52" t="n">
@@ -12161,10 +12173,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="C53" t="n">
@@ -12193,10 +12205,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C54" t="n">
@@ -12225,10 +12237,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44972</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C55" t="n">
@@ -12257,10 +12269,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C56" t="n">
@@ -12289,10 +12301,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45135</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C57" t="n">
@@ -12321,10 +12333,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45232</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="C58" t="n">
@@ -12353,10 +12365,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45341</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C59" t="n">
@@ -12385,10 +12397,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -12417,10 +12429,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C61" t="n">
@@ -12449,10 +12461,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C62" t="n">
@@ -12481,10 +12493,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45708</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C63" t="n">
@@ -12513,10 +12525,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C64" t="n">
@@ -12545,10 +12557,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C65" t="n">
@@ -12577,10 +12589,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C66" t="n">
@@ -12609,10 +12621,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="C67" t="n">
@@ -12641,10 +12653,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C68" t="n">
@@ -12691,12 +12703,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/D.xlsx
+++ b/salidas/empresas/D.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>16.07980537414551</v>
+        <v>16.07980728149414</v>
       </c>
       <c r="C2" t="n">
         <v>37.76499938964844</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.13539886474609</v>
+        <v>16.1353931427002</v>
       </c>
       <c r="C3" t="n">
         <v>37.54999923706055</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.83123970031738</v>
+        <v>14.83124351501465</v>
       </c>
       <c r="C4" t="n">
         <v>34.51499938964844</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.08598327636719</v>
+        <v>16.08597946166992</v>
       </c>
       <c r="C5" t="n">
         <v>37.43500137329102</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.74433040618896</v>
+        <v>15.74433135986328</v>
       </c>
       <c r="C6" t="n">
         <v>36.29000091552734</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>17.02417755126953</v>
+        <v>17.02418327331543</v>
       </c>
       <c r="C8" t="n">
         <v>39.2400016784668</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>17.47834968566895</v>
+        <v>17.47834205627441</v>
       </c>
       <c r="C9" t="n">
         <v>39.94499969482422</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.73449516296387</v>
+        <v>16.73449325561523</v>
       </c>
       <c r="C10" t="n">
         <v>38.24499893188477</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>17.71899032592773</v>
+        <v>17.71900367736816</v>
       </c>
       <c r="C11" t="n">
         <v>40.49499893188477</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.8162784576416</v>
+        <v>17.8162841796875</v>
       </c>
       <c r="C12" t="n">
         <v>40.36999893188477</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>18.50034523010254</v>
+        <v>18.50033760070801</v>
       </c>
       <c r="C13" t="n">
         <v>41.91999816894531</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>18.30615425109863</v>
+        <v>18.3061466217041</v>
       </c>
       <c r="C14" t="n">
         <v>41.47999954223633</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.02981376647949</v>
+        <v>19.02980613708496</v>
       </c>
       <c r="C15" t="n">
         <v>42.76499938964844</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.75069427490234</v>
+        <v>19.75069808959961</v>
       </c>
       <c r="C16" t="n">
         <v>44.3849983215332</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>20.29134559631348</v>
+        <v>20.29134750366211</v>
       </c>
       <c r="C17" t="n">
         <v>45.59999847412109</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>19.87146759033203</v>
+        <v>19.87145805358887</v>
       </c>
       <c r="C18" t="n">
         <v>44.29499816894531</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>18.89123344421387</v>
+        <v>18.8912296295166</v>
       </c>
       <c r="C20" t="n">
         <v>42.11000061035156</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>19.06569290161133</v>
+        <v>19.0656909942627</v>
       </c>
       <c r="C22" t="n">
         <v>42.15000152587891</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>20.72348213195801</v>
+        <v>20.72347831726074</v>
       </c>
       <c r="C23" t="n">
         <v>45.81499862670898</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>21.45479583740234</v>
+        <v>21.45479774475098</v>
       </c>
       <c r="C24" t="n">
         <v>47.22999954223633</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>21.55473709106445</v>
+        <v>21.55473899841309</v>
       </c>
       <c r="C25" t="n">
         <v>47.45000076293945</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>19.53327560424805</v>
+        <v>19.53326797485352</v>
       </c>
       <c r="C26" t="n">
         <v>43</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>18.31243515014648</v>
+        <v>18.31243324279785</v>
       </c>
       <c r="C27" t="n">
         <v>39.93999862670898</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>18.7250804901123</v>
+        <v>18.72508239746094</v>
       </c>
       <c r="C28" t="n">
         <v>40.84000015258789</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>19.89425849914551</v>
+        <v>19.89424705505371</v>
       </c>
       <c r="C29" t="n">
         <v>43.38999938964844</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>21.41438293457031</v>
+        <v>21.41438484191895</v>
       </c>
       <c r="C30" t="n">
         <v>46.29999923706055</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>20.43385314941406</v>
+        <v>20.43386459350586</v>
       </c>
       <c r="C32" t="n">
         <v>44.18000030517578</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>20.31530952453613</v>
+        <v>20.31531143188477</v>
       </c>
       <c r="C33" t="n">
         <v>43.52999877929688</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>19.96528816223145</v>
+        <v>19.96528625488281</v>
       </c>
       <c r="C34" t="n">
         <v>42.77999877929688</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>16.93176460266113</v>
+        <v>16.9317569732666</v>
       </c>
       <c r="C35" t="n">
         <v>36.27999877929688</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.90641784667969</v>
+        <v>16.90642166137695</v>
       </c>
       <c r="C37" t="n">
         <v>35.84000015258789</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>16.59508514404297</v>
+        <v>16.59507942199707</v>
       </c>
       <c r="C38" t="n">
         <v>35.18000030517578</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.43626594543457</v>
+        <v>14.43626308441162</v>
       </c>
       <c r="C39" t="n">
         <v>30.18000030517578</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.82371807098389</v>
+        <v>14.82371711730957</v>
       </c>
       <c r="C40" t="n">
         <v>30.98999977111816</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.42669868469238</v>
+        <v>14.42669582366943</v>
       </c>
       <c r="C41" t="n">
         <v>30.15999984741211</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>15.42047309875488</v>
+        <v>15.42046546936035</v>
       </c>
       <c r="C42" t="n">
         <v>31.79000091552734</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>16.21113586425781</v>
+        <v>16.21113777160645</v>
       </c>
       <c r="C43" t="n">
         <v>33.41999816894531</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.39546775817871</v>
+        <v>16.39546394348145</v>
       </c>
       <c r="C44" t="n">
         <v>33.79999923706055</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>16.25370407104492</v>
+        <v>16.25370788574219</v>
       </c>
       <c r="C45" t="n">
         <v>33.08000183105469</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>16.95141410827637</v>
+        <v>16.95142364501953</v>
       </c>
       <c r="C46" t="n">
         <v>34.5</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.74996948242188</v>
+        <v>16.74996376037598</v>
       </c>
       <c r="C47" t="n">
         <v>34.09000015258789</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.08945655822754</v>
+        <v>18.08946228027344</v>
       </c>
       <c r="C48" t="n">
         <v>36.38000106811523</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.35244941711426</v>
+        <v>19.35243988037109</v>
       </c>
       <c r="C49" t="n">
         <v>38.91999816894531</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.6264820098877</v>
+        <v>18.62647819519043</v>
       </c>
       <c r="C50" t="n">
         <v>37.45999908447266</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>19.11553764343262</v>
+        <v>19.11553955078125</v>
       </c>
       <c r="C51" t="n">
         <v>37.9900016784668</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.6854362487793</v>
+        <v>20.68543815612793</v>
       </c>
       <c r="C52" t="n">
         <v>41.11000061035156</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>21.03262710571289</v>
+        <v>21.03262519836426</v>
       </c>
       <c r="C53" t="n">
         <v>41.79999923706055</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>19.83519172668457</v>
+        <v>19.83517837524414</v>
       </c>
       <c r="C54" t="n">
         <v>38.95999908447266</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>19.72318458557129</v>
+        <v>19.72318077087402</v>
       </c>
       <c r="C55" t="n">
         <v>38.7400016784668</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>21.3778133392334</v>
+        <v>21.37781143188477</v>
       </c>
       <c r="C56" t="n">
         <v>41.9900016784668</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>21.98125076293945</v>
+        <v>21.98125267028809</v>
       </c>
       <c r="C57" t="n">
         <v>42.72999954223633</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>22.45966529846191</v>
+        <v>22.45966148376465</v>
       </c>
       <c r="C58" t="n">
         <v>43.65999984741211</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>22.35677528381348</v>
+        <v>22.35677337646484</v>
       </c>
       <c r="C59" t="n">
         <v>43.45999908447266</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>21.59674263000488</v>
+        <v>21.59672927856445</v>
       </c>
       <c r="C60" t="n">
         <v>41.52999877929688</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>22.21557235717773</v>
+        <v>22.2155590057373</v>
       </c>
       <c r="C61" t="n">
         <v>42.72000122070312</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>22.64198875427246</v>
+        <v>22.64198684692383</v>
       </c>
       <c r="C62" t="n">
         <v>43.54000091552734</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>23.72884368896484</v>
+        <v>23.72884941101074</v>
       </c>
       <c r="C63" t="n">
         <v>45.63000106811523</v>
@@ -1796,7 +1796,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>23.49944114685059</v>
+        <v>23.49944305419922</v>
       </c>
       <c r="C64" t="n">
         <v>44.70000076293945</v>
@@ -1821,7 +1821,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>24.40368270874023</v>
+        <v>24.40367698669434</v>
       </c>
       <c r="C65" t="n">
         <v>46.41999816894531</v>
@@ -1850,7 +1850,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>25.34794235229492</v>
+        <v>25.34793472290039</v>
       </c>
       <c r="C66" t="n">
         <v>47.72000122070312</v>
@@ -1879,7 +1879,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>25.64008331298828</v>
+        <v>25.64009475708008</v>
       </c>
       <c r="C67" t="n">
         <v>48.27000045776367</v>
@@ -1908,7 +1908,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>25.7357063293457</v>
+        <v>25.7357006072998</v>
       </c>
       <c r="C68" t="n">
         <v>48.45000076293945</v>
@@ -1937,7 +1937,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>26.15233039855957</v>
+        <v>26.15232849121094</v>
       </c>
       <c r="C69" t="n">
         <v>48.7400016784668</v>
@@ -1966,7 +1966,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>27.24157333374023</v>
+        <v>27.24156761169434</v>
       </c>
       <c r="C70" t="n">
         <v>50.77000045776367</v>
@@ -1995,7 +1995,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>27.68156051635742</v>
+        <v>27.68155860900879</v>
       </c>
       <c r="C71" t="n">
         <v>51.59000015258789</v>
@@ -2024,7 +2024,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.96881866455078</v>
+        <v>27.96881294250488</v>
       </c>
       <c r="C72" t="n">
         <v>51.61999893188477</v>
@@ -2053,7 +2053,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>28.75988578796387</v>
+        <v>28.75988006591797</v>
       </c>
       <c r="C73" t="n">
         <v>53.08000183105469</v>
@@ -2111,7 +2111,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>27.6303768157959</v>
+        <v>27.6303825378418</v>
       </c>
       <c r="C75" t="n">
         <v>50.47000122070312</v>
@@ -2140,7 +2140,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>28.0355052947998</v>
+        <v>28.03549957275391</v>
       </c>
       <c r="C76" t="n">
         <v>51.20999908447266</v>
@@ -2169,7 +2169,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>28.5720100402832</v>
+        <v>28.57200813293457</v>
       </c>
       <c r="C77" t="n">
         <v>52.18999862670898</v>
@@ -2198,7 +2198,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>28.79038429260254</v>
+        <v>28.79040336608887</v>
       </c>
       <c r="C78" t="n">
         <v>52.06000137329102</v>
@@ -2227,7 +2227,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>29.86326026916504</v>
+        <v>29.86326599121094</v>
       </c>
       <c r="C79" t="n">
         <v>54</v>
@@ -2256,7 +2256,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>30.03469657897949</v>
+        <v>30.03469848632812</v>
       </c>
       <c r="C80" t="n">
         <v>54.31000137329102</v>
@@ -2314,7 +2314,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>29.56641578674316</v>
+        <v>29.56641387939453</v>
       </c>
       <c r="C82" t="n">
         <v>52.93999862670898</v>
@@ -2343,7 +2343,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>29.47707176208496</v>
+        <v>29.47706413269043</v>
       </c>
       <c r="C83" t="n">
         <v>52.77999877929688</v>
@@ -2401,7 +2401,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>29.23457717895508</v>
+        <v>29.23457527160645</v>
       </c>
       <c r="C85" t="n">
         <v>51.79999923706055</v>
@@ -2430,7 +2430,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>30.53828620910645</v>
+        <v>30.53827476501465</v>
       </c>
       <c r="C86" t="n">
         <v>54.11000061035156</v>
@@ -2459,7 +2459,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>31.92761039733887</v>
+        <v>31.92759895324707</v>
       </c>
       <c r="C87" t="n">
         <v>56</v>
@@ -2488,7 +2488,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>33.17050170898438</v>
+        <v>33.17049407958984</v>
       </c>
       <c r="C88" t="n">
         <v>58.18000030517578</v>
@@ -2546,7 +2546,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>32.24117660522461</v>
+        <v>32.24117279052734</v>
       </c>
       <c r="C90" t="n">
         <v>56.54999923706055</v>
@@ -2575,7 +2575,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>32.72615051269531</v>
+        <v>32.72614288330078</v>
       </c>
       <c r="C91" t="n">
         <v>56.81999969482422</v>
@@ -2633,7 +2633,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>33.60735702514648</v>
+        <v>33.60736083984375</v>
       </c>
       <c r="C93" t="n">
         <v>58.34999847412109</v>
@@ -2662,7 +2662,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>36.34017562866211</v>
+        <v>36.34018325805664</v>
       </c>
       <c r="C94" t="n">
         <v>62.47999954223633</v>
@@ -2691,7 +2691,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>37.07884979248047</v>
+        <v>37.07884216308594</v>
       </c>
       <c r="C95" t="n">
         <v>63.75</v>
@@ -2720,7 +2720,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>37.7535400390625</v>
+        <v>37.75353240966797</v>
       </c>
       <c r="C96" t="n">
         <v>64.91000366210938</v>
@@ -2749,7 +2749,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>37.95540618896484</v>
+        <v>37.95539855957031</v>
       </c>
       <c r="C97" t="n">
         <v>64.69000244140625</v>
@@ -2778,7 +2778,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>39.84466171264648</v>
+        <v>39.84465789794922</v>
       </c>
       <c r="C98" t="n">
         <v>67.91000366210938</v>
@@ -2807,7 +2807,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>41.06462478637695</v>
+        <v>41.06465148925781</v>
       </c>
       <c r="C99" t="n">
         <v>69.40000152587891</v>
@@ -2836,7 +2836,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>42.00545883178711</v>
+        <v>42.00545501708984</v>
       </c>
       <c r="C100" t="n">
         <v>70.98999786376953</v>
@@ -2865,7 +2865,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>42.92262649536133</v>
+        <v>42.922607421875</v>
       </c>
       <c r="C101" t="n">
         <v>72.54000091552734</v>
@@ -2894,7 +2894,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>41.16003036499023</v>
+        <v>41.16001892089844</v>
       </c>
       <c r="C102" t="n">
         <v>68.95999908447266</v>
@@ -2923,7 +2923,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>42.68801879882812</v>
+        <v>42.68802642822266</v>
       </c>
       <c r="C103" t="n">
         <v>71.51999664306641</v>
@@ -2952,7 +2952,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>40.37217712402344</v>
+        <v>40.37216949462891</v>
       </c>
       <c r="C104" t="n">
         <v>67.63999938964844</v>
@@ -2981,7 +2981,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>42.27743530273438</v>
+        <v>42.27744293212891</v>
       </c>
       <c r="C105" t="n">
         <v>70.22000122070312</v>
@@ -3010,7 +3010,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>41.59710311889648</v>
+        <v>41.59709167480469</v>
       </c>
       <c r="C106" t="n">
         <v>69.08999633789062</v>
@@ -3068,7 +3068,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>44.04201889038086</v>
+        <v>44.04201507568359</v>
       </c>
       <c r="C108" t="n">
         <v>72.55000305175781</v>
@@ -3126,7 +3126,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>46.67665863037109</v>
+        <v>46.67664337158203</v>
       </c>
       <c r="C110" t="n">
         <v>76.88999938964844</v>
@@ -3155,7 +3155,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>44.14904403686523</v>
+        <v>44.1490364074707</v>
       </c>
       <c r="C111" t="n">
         <v>72.08999633789062</v>
@@ -3184,7 +3184,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>43.40190887451172</v>
+        <v>43.40190505981445</v>
       </c>
       <c r="C112" t="n">
         <v>70.87000274658203</v>
@@ -3213,7 +3213,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>43.89797210693359</v>
+        <v>43.89796447753906</v>
       </c>
       <c r="C113" t="n">
         <v>71.68000030517578</v>
@@ -3271,7 +3271,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>41.32674789428711</v>
+        <v>41.32674026489258</v>
       </c>
       <c r="C115" t="n">
         <v>66.87000274658203</v>
@@ -3329,7 +3329,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>43.50806427001953</v>
+        <v>43.50806045532227</v>
       </c>
       <c r="C117" t="n">
         <v>69.75</v>
@@ -3358,7 +3358,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>43.90103530883789</v>
+        <v>43.90103149414062</v>
       </c>
       <c r="C118" t="n">
         <v>70.37999725341797</v>
@@ -3387,7 +3387,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>44.55599212646484</v>
+        <v>44.55600357055664</v>
       </c>
       <c r="C119" t="n">
         <v>71.43000030517578</v>
@@ -3416,7 +3416,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>42.4218864440918</v>
+        <v>42.42187118530273</v>
       </c>
       <c r="C120" t="n">
         <v>67.37000274658203</v>
@@ -3445,7 +3445,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>42.59188461303711</v>
+        <v>42.59189224243164</v>
       </c>
       <c r="C121" t="n">
         <v>67.63999938964844</v>
@@ -3474,7 +3474,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>45.44436645507812</v>
+        <v>45.44437789916992</v>
       </c>
       <c r="C122" t="n">
         <v>72.16999816894531</v>
@@ -3503,7 +3503,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>44.02758026123047</v>
+        <v>44.02756881713867</v>
       </c>
       <c r="C123" t="n">
         <v>69.91999816894531</v>
@@ -3532,7 +3532,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>47.78009033203125</v>
+        <v>47.78007888793945</v>
       </c>
       <c r="C124" t="n">
         <v>75.12000274658203</v>
@@ -3561,7 +3561,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>45.4585075378418</v>
+        <v>45.45851516723633</v>
       </c>
       <c r="C125" t="n">
         <v>71.47000122070312</v>
@@ -3590,7 +3590,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>45.95461654663086</v>
+        <v>45.95461273193359</v>
       </c>
       <c r="C126" t="n">
         <v>72.25</v>
@@ -3619,7 +3619,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>50.05231475830078</v>
+        <v>50.05232620239258</v>
       </c>
       <c r="C127" t="n">
         <v>77.93000030517578</v>
@@ -3648,7 +3648,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>50.11013412475586</v>
+        <v>50.11013031005859</v>
       </c>
       <c r="C128" t="n">
         <v>78.01999664306641</v>
@@ -3677,7 +3677,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>48.07998657226562</v>
+        <v>48.08000183105469</v>
       </c>
       <c r="C129" t="n">
         <v>74.16000366210938</v>
@@ -3735,7 +3735,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>48.75425338745117</v>
+        <v>48.75424575805664</v>
       </c>
       <c r="C131" t="n">
         <v>75.19999694824219</v>
@@ -3764,7 +3764,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>47.95702743530273</v>
+        <v>47.95703887939453</v>
       </c>
       <c r="C132" t="n">
         <v>73.29000091552734</v>
@@ -3793,7 +3793,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>50.11635208129883</v>
+        <v>50.11635971069336</v>
       </c>
       <c r="C133" t="n">
         <v>76.58999633789062</v>
@@ -3822,7 +3822,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>49.91352081298828</v>
+        <v>49.91351699829102</v>
       </c>
       <c r="C134" t="n">
         <v>76.27999877929688</v>
@@ -3851,7 +3851,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>50.80342483520508</v>
+        <v>50.80343246459961</v>
       </c>
       <c r="C135" t="n">
         <v>77.63999938964844</v>
@@ -3880,7 +3880,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>51.25605773925781</v>
+        <v>51.25605392456055</v>
       </c>
       <c r="C136" t="n">
         <v>77.56999969482422</v>
@@ -3909,7 +3909,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>51.16355133056641</v>
+        <v>51.16353988647461</v>
       </c>
       <c r="C137" t="n">
         <v>77.43000030517578</v>
@@ -3938,7 +3938,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>53.87254333496094</v>
+        <v>53.87255477905273</v>
       </c>
       <c r="C138" t="n">
         <v>80.76999664306641</v>
@@ -3967,7 +3967,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>51.11121368408203</v>
+        <v>51.1112174987793</v>
       </c>
       <c r="C139" t="n">
         <v>76.62999725341797</v>
@@ -3996,7 +3996,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>51.47806549072266</v>
+        <v>51.47805404663086</v>
       </c>
       <c r="C140" t="n">
         <v>77.18000030517578</v>
@@ -4025,7 +4025,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>53.03762817382812</v>
+        <v>53.03762054443359</v>
       </c>
       <c r="C141" t="n">
         <v>78.76999664306641</v>
@@ -4054,7 +4054,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>51.7987060546875</v>
+        <v>51.79870986938477</v>
       </c>
       <c r="C142" t="n">
         <v>76.93000030517578</v>
@@ -4083,7 +4083,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>54.63340377807617</v>
+        <v>54.63338851928711</v>
       </c>
       <c r="C143" t="n">
         <v>81.13999938964844</v>
@@ -4112,7 +4112,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>57.17068099975586</v>
+        <v>57.17069625854492</v>
       </c>
       <c r="C144" t="n">
         <v>84.12999725341797</v>
@@ -4141,7 +4141,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>55.08445739746094</v>
+        <v>55.08446884155273</v>
       </c>
       <c r="C145" t="n">
         <v>81.05999755859375</v>
@@ -4170,7 +4170,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>51.94493865966797</v>
+        <v>51.9449462890625</v>
       </c>
       <c r="C146" t="n">
         <v>76.44000244140625</v>
@@ -4199,7 +4199,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>50.33440399169922</v>
+        <v>50.33441162109375</v>
       </c>
       <c r="C147" t="n">
         <v>74.06999969482422</v>
@@ -4228,7 +4228,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>46.34463500976562</v>
+        <v>46.34461975097656</v>
       </c>
       <c r="C148" t="n">
         <v>67.43000030517578</v>
@@ -4257,7 +4257,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>45.74667358398438</v>
+        <v>45.74667739868164</v>
       </c>
       <c r="C149" t="n">
         <v>66.55999755859375</v>
@@ -4286,7 +4286,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>44.69621276855469</v>
+        <v>44.69621658325195</v>
       </c>
       <c r="C150" t="n">
         <v>64.19000244140625</v>
@@ -4315,7 +4315,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>47.47449493408203</v>
+        <v>47.47450256347656</v>
       </c>
       <c r="C151" t="n">
         <v>68.18000030517578</v>
@@ -4344,7 +4344,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>49.93248748779297</v>
+        <v>49.93247604370117</v>
       </c>
       <c r="C152" t="n">
         <v>71.70999908447266</v>
@@ -4373,7 +4373,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>49.27795791625977</v>
+        <v>49.27795028686523</v>
       </c>
       <c r="C153" t="n">
         <v>70.76999664306641</v>
@@ -4402,7 +4402,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>49.50734710693359</v>
+        <v>49.50734329223633</v>
       </c>
       <c r="C154" t="n">
         <v>70.27999877929688</v>
@@ -4431,7 +4431,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>50.31039810180664</v>
+        <v>50.31037521362305</v>
       </c>
       <c r="C155" t="n">
         <v>71.41999816894531</v>
@@ -4460,7 +4460,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>52.48002624511719</v>
+        <v>52.48004531860352</v>
       </c>
       <c r="C156" t="n">
         <v>74.5</v>
@@ -4489,7 +4489,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>50.90288162231445</v>
+        <v>50.90289306640625</v>
       </c>
       <c r="C157" t="n">
         <v>71.45999908447266</v>
@@ -4518,7 +4518,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>50.03383255004883</v>
+        <v>50.03382873535156</v>
       </c>
       <c r="C158" t="n">
         <v>70.23999786376953</v>
@@ -4547,7 +4547,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>53.43624496459961</v>
+        <v>53.43624877929688</v>
       </c>
       <c r="C159" t="n">
         <v>74.08999633789062</v>
@@ -4576,7 +4576,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>55.28983688354492</v>
+        <v>55.28983306884766</v>
       </c>
       <c r="C160" t="n">
         <v>76.66000366210938</v>
@@ -4605,7 +4605,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>56.16250610351562</v>
+        <v>56.16252136230469</v>
       </c>
       <c r="C161" t="n">
         <v>77.87000274658203</v>
@@ -4634,7 +4634,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>54.22240829467773</v>
+        <v>54.22241592407227</v>
       </c>
       <c r="C162" t="n">
         <v>75.18000030517578</v>
@@ -4692,7 +4692,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>54.22185897827148</v>
+        <v>54.22187042236328</v>
       </c>
       <c r="C164" t="n">
         <v>74.29000091552734</v>
@@ -4721,7 +4721,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>56.65961074829102</v>
+        <v>56.65961456298828</v>
       </c>
       <c r="C165" t="n">
         <v>77.62999725341797</v>
@@ -4750,7 +4750,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>59.84254837036133</v>
+        <v>59.842529296875</v>
       </c>
       <c r="C166" t="n">
         <v>81.04000091552734</v>
@@ -4779,7 +4779,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>60.95756530761719</v>
+        <v>60.95755386352539</v>
       </c>
       <c r="C167" t="n">
         <v>82.55000305175781</v>
@@ -4808,7 +4808,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>61.3710823059082</v>
+        <v>61.37108612060547</v>
       </c>
       <c r="C168" t="n">
         <v>83.11000061035156</v>
@@ -4837,7 +4837,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>61.84721755981445</v>
+        <v>61.84722518920898</v>
       </c>
       <c r="C169" t="n">
         <v>82.81999969482422</v>
@@ -4866,7 +4866,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>64.03525543212891</v>
+        <v>64.03524780273438</v>
       </c>
       <c r="C170" t="n">
         <v>85.75</v>
@@ -4895,7 +4895,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>59.02162170410156</v>
+        <v>59.02164077758789</v>
       </c>
       <c r="C171" t="n">
         <v>78.18000030517578</v>
@@ -4924,7 +4924,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>54.49948883056641</v>
+        <v>54.49949264526367</v>
       </c>
       <c r="C172" t="n">
         <v>72.19000244140625</v>
@@ -4953,7 +4953,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>58.22892379760742</v>
+        <v>58.22893142700195</v>
       </c>
       <c r="C173" t="n">
         <v>77.12999725341797</v>
@@ -5011,7 +5011,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>61.95994186401367</v>
+        <v>61.95993804931641</v>
       </c>
       <c r="C175" t="n">
         <v>81.18000030517578</v>
@@ -5040,7 +5040,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>61.84543609619141</v>
+        <v>61.84544372558594</v>
       </c>
       <c r="C176" t="n">
         <v>81.02999877929688</v>
@@ -5069,7 +5069,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>59.8686637878418</v>
+        <v>59.86864471435547</v>
       </c>
       <c r="C177" t="n">
         <v>78.44000244140625</v>
@@ -5098,7 +5098,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>60.96255493164062</v>
+        <v>60.96255111694336</v>
       </c>
       <c r="C178" t="n">
         <v>78.93000030517578</v>
@@ -5127,7 +5127,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>62.05157089233398</v>
+        <v>62.05158615112305</v>
       </c>
       <c r="C179" t="n">
         <v>80.33999633789062</v>
@@ -5156,7 +5156,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>60.62272262573242</v>
+        <v>60.62270355224609</v>
       </c>
       <c r="C180" t="n">
         <v>78.48999786376953</v>
@@ -5183,7 +5183,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>58.54104232788086</v>
+        <v>58.54103469848633</v>
       </c>
       <c r="C181" t="n">
         <v>75.19999694824219</v>
@@ -5210,7 +5210,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>56.74276733398438</v>
+        <v>56.74275970458984</v>
       </c>
       <c r="C182" t="n">
         <v>72.88999938964844</v>
@@ -5237,7 +5237,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>53.18517303466797</v>
+        <v>53.1851692199707</v>
       </c>
       <c r="C183" t="n">
         <v>68.31999969482422</v>
@@ -5264,7 +5264,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>59.67296600341797</v>
+        <v>59.6729850769043</v>
       </c>
       <c r="C184" t="n">
         <v>75.95999908447266</v>
@@ -5291,7 +5291,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>62.76816940307617</v>
+        <v>62.76819229125977</v>
       </c>
       <c r="C185" t="n">
         <v>79.90000152587891</v>
@@ -5318,7 +5318,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>59.81438446044922</v>
+        <v>59.81436920166016</v>
       </c>
       <c r="C186" t="n">
         <v>76.13999938964844</v>
@@ -5347,7 +5347,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>58.27603530883789</v>
+        <v>58.27604293823242</v>
       </c>
       <c r="C187" t="n">
         <v>73.56999969482422</v>
@@ -5376,7 +5376,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>59.30579376220703</v>
+        <v>59.30580139160156</v>
       </c>
       <c r="C188" t="n">
         <v>74.87000274658203</v>
@@ -5405,7 +5405,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>61.65838623046875</v>
+        <v>61.65839385986328</v>
       </c>
       <c r="C189" t="n">
         <v>77.83999633789062</v>
@@ -5463,7 +5463,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>60.62905502319336</v>
+        <v>60.62907409667969</v>
       </c>
       <c r="C191" t="n">
         <v>75.93000030517578</v>
@@ -5521,7 +5521,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>63.29186248779297</v>
+        <v>63.29186630249023</v>
       </c>
       <c r="C193" t="n">
         <v>78.55999755859375</v>
@@ -5550,7 +5550,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>64.98374176025391</v>
+        <v>64.98373413085938</v>
       </c>
       <c r="C194" t="n">
         <v>80.66000366210938</v>
@@ -5579,7 +5579,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>64.07334899902344</v>
+        <v>64.07334136962891</v>
       </c>
       <c r="C195" t="n">
         <v>79.52999877929688</v>
@@ -5608,7 +5608,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>69.03134918212891</v>
+        <v>69.03135681152344</v>
       </c>
       <c r="C196" t="n">
         <v>84.97000122070312</v>
@@ -5637,7 +5637,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>66.32599639892578</v>
+        <v>66.32598114013672</v>
       </c>
       <c r="C197" t="n">
         <v>81.63999938964844</v>
@@ -5666,7 +5666,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>68.42203521728516</v>
+        <v>68.42202758789062</v>
       </c>
       <c r="C198" t="n">
         <v>84.22000122070312</v>
@@ -5695,7 +5695,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>65.36082458496094</v>
+        <v>65.36083221435547</v>
       </c>
       <c r="C199" t="n">
         <v>79.80999755859375</v>
@@ -5724,7 +5724,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>67.13798522949219</v>
+        <v>67.13796234130859</v>
       </c>
       <c r="C200" t="n">
         <v>81.98000335693359</v>
@@ -5753,7 +5753,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>66.99056243896484</v>
+        <v>66.99054718017578</v>
       </c>
       <c r="C201" t="n">
         <v>81.80000305175781</v>
@@ -5782,7 +5782,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>57.06401062011719</v>
+        <v>57.06399917602539</v>
       </c>
       <c r="C202" t="n">
         <v>69.11000061035156</v>
@@ -5811,7 +5811,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>57.77410125732422</v>
+        <v>57.77410507202148</v>
       </c>
       <c r="C203" t="n">
         <v>69.97000122070312</v>
@@ -5840,7 +5840,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>50.45841979980469</v>
+        <v>50.45842742919922</v>
       </c>
       <c r="C204" t="n">
         <v>61.11000061035156</v>
@@ -5869,7 +5869,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>51.19140625</v>
+        <v>51.19139862060547</v>
       </c>
       <c r="C205" t="n">
         <v>61.31999969482422</v>
@@ -5956,7 +5956,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>47.25161743164062</v>
+        <v>47.25162124633789</v>
       </c>
       <c r="C208" t="n">
         <v>55.90999984741211</v>
@@ -5985,7 +5985,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>48.29114532470703</v>
+        <v>48.29113388061523</v>
       </c>
       <c r="C209" t="n">
         <v>57.13999938964844</v>
@@ -6159,7 +6159,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>35.00716018676758</v>
+        <v>35.00717163085938</v>
       </c>
       <c r="C215" t="n">
         <v>40.31999969482422</v>
@@ -6188,7 +6188,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>39.93659210205078</v>
+        <v>39.93658447265625</v>
       </c>
       <c r="C216" t="n">
         <v>45.34000015258789</v>
@@ -6246,7 +6246,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>40.27129745483398</v>
+        <v>40.27130126953125</v>
       </c>
       <c r="C218" t="n">
         <v>45.72000122070312</v>
@@ -6275,7 +6275,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>42.72005844116211</v>
+        <v>42.72006607055664</v>
       </c>
       <c r="C219" t="n">
         <v>47.83000183105469</v>
@@ -6304,7 +6304,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>43.93475723266602</v>
+        <v>43.93476104736328</v>
       </c>
       <c r="C220" t="n">
         <v>49.18999862670898</v>
@@ -6333,7 +6333,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>45.53351974487305</v>
+        <v>45.53353118896484</v>
       </c>
       <c r="C221" t="n">
         <v>50.97999954223633</v>
@@ -6391,7 +6391,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>44.31842422485352</v>
+        <v>44.31842041015625</v>
       </c>
       <c r="C223" t="n">
         <v>49</v>
@@ -6449,7 +6449,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>51.16823959350586</v>
+        <v>51.16823577880859</v>
       </c>
       <c r="C225" t="n">
         <v>55.90000152587891</v>
@@ -6478,7 +6478,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>52.89824676513672</v>
+        <v>52.89825057983398</v>
       </c>
       <c r="C226" t="n">
         <v>57.79000091552734</v>
@@ -6536,7 +6536,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>54.38553237915039</v>
+        <v>54.38552474975586</v>
       </c>
       <c r="C228" t="n">
         <v>58.75</v>
@@ -6565,7 +6565,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>49.85879516601562</v>
+        <v>49.85879898071289</v>
       </c>
       <c r="C229" t="n">
         <v>53.86000061035156</v>
@@ -6623,7 +6623,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>53.04108810424805</v>
+        <v>53.04108428955078</v>
       </c>
       <c r="C231" t="n">
         <v>56.61999893188477</v>
@@ -6652,7 +6652,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>52.52585220336914</v>
+        <v>52.52584838867188</v>
       </c>
       <c r="C232" t="n">
         <v>56.06999969482422</v>
@@ -6681,7 +6681,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>50.94268035888672</v>
+        <v>50.94267654418945</v>
       </c>
       <c r="C233" t="n">
         <v>54.38000106811523</v>
@@ -6739,7 +6739,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>53.58800888061523</v>
+        <v>53.58800506591797</v>
       </c>
       <c r="C235" t="n">
         <v>56.52000045776367</v>
@@ -6826,7 +6826,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>58.66335296630859</v>
+        <v>58.66334915161133</v>
       </c>
       <c r="C238" t="n">
         <v>61.16999816894531</v>
@@ -6855,7 +6855,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>56.28497695922852</v>
+        <v>56.28497314453125</v>
       </c>
       <c r="C239" t="n">
         <v>58.68999862670898</v>
@@ -6884,7 +6884,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>60.19778442382812</v>
+        <v>60.19778823852539</v>
       </c>
       <c r="C240" t="n">
         <v>62.77000045776367</v>
@@ -6913,7 +6913,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>56.82339859008789</v>
+        <v>56.82340240478516</v>
       </c>
       <c r="C241" t="n">
         <v>58.59000015258789</v>
@@ -6942,7 +6942,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>58.35575866699219</v>
+        <v>58.35576248168945</v>
       </c>
       <c r="C242" t="n">
         <v>60.16999816894531</v>
@@ -7029,7 +7029,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>63.22185134887695</v>
+        <v>63.22185516357422</v>
       </c>
       <c r="C245" t="n">
         <v>64.5</v>
